--- a/PY_pytest/TutuorialNinja_DataDriven/Excel/Book1.xlsx
+++ b/PY_pytest/TutuorialNinja_DataDriven/Excel/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python selenium-D\PY_pytest\TutuorialNinja_DataDriven\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70165040-6190-428F-B669-A4C5CF6F400A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CF53C9-1E17-4958-9A59-64C94AA98013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2385" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{04688EDC-C1A9-40DB-8040-96C96F39DAF7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{04688EDC-C1A9-40DB-8040-96C96F39DAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/PY_pytest/TutuorialNinja_DataDriven/Excel/Book1.xlsx
+++ b/PY_pytest/TutuorialNinja_DataDriven/Excel/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python selenium-D\PY_pytest\TutuorialNinja_DataDriven\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CF53C9-1E17-4958-9A59-64C94AA98013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF73C74-D99F-4B37-8F67-B30B4189E418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{04688EDC-C1A9-40DB-8040-96C96F39DAF7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{04688EDC-C1A9-40DB-8040-96C96F39DAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>userName</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>canon</t>
+  </si>
+  <si>
+    <t>aakash123</t>
   </si>
 </sst>
 </file>
@@ -431,7 +434,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
